--- a/database/test.xlsx
+++ b/database/test.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -558,94 +558,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EM105454</t>
+          <t>S104959</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VERTICAL PLATE CLAMP: 1.5t Suitable for Range 0-20mm Serial Number: 11089735</t>
+          <t>Manual Chain Block : 250kg x 3m Tiger Model TCB14 Hook Suspension with 3m Chain Fall 5% Light Load Test Applied Original E.C. Declaration Cert No. 0000028944 Colour Code: Green</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RS-N238396-2</t>
+          <t>SB343913</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8th May 2024</t>
+          <t>01/09/2023</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>07/12/24</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>LOFT-RS-N217016</t>
+          <t>LOFT-SJB110523</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
-        <is>
-          <t>[FileNotFoundError(2, 'No such file or directory'), 'page no: 1']</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EM38861</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Beam Clamp Model: S3A Suitable for Flange Range 150mm – 305mm Serial Number: R059748</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RS-N238396-3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>8th May 2024</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>07/12/24</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>LOFT-RS-N227196</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
         <is>
           <t>[FileNotFoundError(2, 'No such file or directory'), 'page no: 2']</t>
         </is>
